--- a/Produce/xls/技能配置表.xlsx
+++ b/Produce/xls/技能配置表.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15071" windowHeight="4487"/>
+    <workbookView windowWidth="28095" windowHeight="12495"/>
   </bookViews>
   <sheets>
-    <sheet name="技能基础配置表" sheetId="1" r:id="rId1"/>
+    <sheet name="SkillBaseConfig" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>ID</t>
   </si>
@@ -22,10 +22,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>BuffID_1</t>
-  </si>
-  <si>
-    <t>BuffID_2</t>
+    <t>BuffIDArray</t>
+  </si>
+  <si>
+    <t>DescArray</t>
+  </si>
+  <si>
+    <t>#屏蔽不转</t>
   </si>
   <si>
     <t>int</t>
@@ -40,7 +43,25 @@
     <t>技能名称</t>
   </si>
   <si>
+    <t>BuffID数组</t>
+  </si>
+  <si>
+    <t>描述数组</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>蓄力一击</t>
+  </si>
+  <si>
+    <t>[10001,10002]</t>
+  </si>
+  <si>
+    <t>["芜湖","起飞"]</t>
+  </si>
+  <si>
+    <t>双倍伤害</t>
   </si>
 </sst>
 </file>
@@ -48,12 +69,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,11 +83,94 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -78,89 +182,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -169,6 +190,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -176,6 +206,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
@@ -183,22 +228,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
@@ -206,7 +235,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -215,12 +244,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -233,7 +298,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,31 +358,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -281,37 +382,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -323,13 +400,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -341,55 +418,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -406,15 +441,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -429,6 +455,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -466,17 +501,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -506,6 +532,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -514,10 +549,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -526,139 +561,142 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1011,15 +1049,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="24" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.8888888888889" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="24" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.8916666666667" style="2" customWidth="1"/>
+    <col min="3" max="4" width="28.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.875" style="2" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1032,47 +1072,56 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1">
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
         <v>1001</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1">
-        <v>10001</v>
-      </c>
-      <c r="D4" s="1">
-        <v>10002</v>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/Produce/xls/技能配置表.xlsx
+++ b/Produce/xls/技能配置表.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28095" windowHeight="12495"/>
+    <workbookView windowWidth="15071" windowHeight="4487"/>
   </bookViews>
   <sheets>
-    <sheet name="SkillBaseConfig" sheetId="1" r:id="rId1"/>
+    <sheet name="技能基础配置表" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>ID</t>
   </si>
@@ -22,13 +22,10 @@
     <t>Name</t>
   </si>
   <si>
-    <t>BuffIDArray</t>
+    <t>BuffID_1</t>
   </si>
   <si>
-    <t>DescArray</t>
-  </si>
-  <si>
-    <t>#屏蔽不转</t>
+    <t>BuffID_2</t>
   </si>
   <si>
     <t>int</t>
@@ -43,25 +40,7 @@
     <t>技能名称</t>
   </si>
   <si>
-    <t>BuffID数组</t>
-  </si>
-  <si>
-    <t>描述数组</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
     <t>蓄力一击</t>
-  </si>
-  <si>
-    <t>[10001,10002]</t>
-  </si>
-  <si>
-    <t>["芜湖","起飞"]</t>
-  </si>
-  <si>
-    <t>双倍伤害</t>
   </si>
 </sst>
 </file>
@@ -69,12 +48,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,86 +62,71 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -174,11 +138,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -190,6 +169,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -200,14 +193,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
@@ -215,27 +200,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -244,7 +215,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -256,7 +287,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -268,37 +317,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -310,121 +389,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,6 +406,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -455,15 +429,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -501,8 +466,17 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -532,15 +506,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -549,10 +514,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -561,142 +526,139 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1049,17 +1011,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="24" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.8916666666667" style="2" customWidth="1"/>
-    <col min="3" max="4" width="28.25" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="2" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="24" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.8888888888889" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1072,56 +1032,47 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>6</v>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" s="1">
+        <v>1001</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
+      <c r="C4" s="1">
+        <v>10001</v>
+      </c>
+      <c r="D4" s="1">
+        <v>10002</v>
       </c>
     </row>
   </sheetData>
